--- a/artfynd/A 21088-2026 artfynd.xlsx
+++ b/artfynd/A 21088-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97338087</v>
+        <v>97337940</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560579.9188319806</v>
+        <v>560580</v>
       </c>
       <c r="R2" t="n">
-        <v>6842103.907651271</v>
+        <v>6842104</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2021-11-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97337940</v>
+        <v>99622545</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,31 +796,33 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Badtjärn, Hls</t>
+          <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560579.9188319806</v>
+        <v>560619</v>
       </c>
       <c r="R3" t="n">
-        <v>6842103.907651271</v>
+        <v>6842091</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99622545</v>
+        <v>99641088</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,17 +898,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -952,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560619.091916354</v>
+        <v>560579</v>
       </c>
       <c r="R4" t="n">
-        <v>6842091.788913677</v>
+        <v>6842133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,29 +948,29 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1024,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99622551</v>
+        <v>97338087</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,25 +1018,23 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusdal, Hls</t>
+          <t>Badtjärn, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560619.091916354</v>
+        <v>560580</v>
       </c>
       <c r="R5" t="n">
-        <v>6842091.788913677</v>
+        <v>6842104</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99622573</v>
+        <v>99622551</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560626.3084107362</v>
+        <v>560619</v>
       </c>
       <c r="R6" t="n">
-        <v>6842086.69767757</v>
+        <v>6842091</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,19 +1164,9 @@
           <t>2022-04-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99641304</v>
+        <v>99622573</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1221,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560692.4594217013</v>
+        <v>560626</v>
       </c>
       <c r="R7" t="n">
-        <v>6842134.355045194</v>
+        <v>6842086</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,22 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99638004</v>
+        <v>99637452</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560583.5787596316</v>
+        <v>560573</v>
       </c>
       <c r="R8" t="n">
-        <v>6842057.955186703</v>
+        <v>6842148</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1366,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1376,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,52 +1403,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99638154</v>
+        <v>99638004</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560589.3953989896</v>
+        <v>560583</v>
       </c>
       <c r="R9" t="n">
-        <v>6842051.415955768</v>
+        <v>6842058</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1561,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,15 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99641088</v>
+        <v>99641304</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,28 +1522,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1643,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560579.4010557401</v>
+        <v>560692</v>
       </c>
       <c r="R10" t="n">
-        <v>6842133.311085386</v>
+        <v>6842135</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1678,7 +1582,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,14 +1592,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1715,15 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99637452</v>
+        <v>98469922</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,38 +1630,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ljusdal, Hls</t>
+          <t>Badtjärn, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560573.442613819</v>
+        <v>560580</v>
       </c>
       <c r="R11" t="n">
-        <v>6842147.91234732</v>
+        <v>6842104</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,22 +1688,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hej! Jag publicerar här några bilder på vad jag tror indikerar på aktivitet av tretåig hackspett. Min bror hittade 6 bohål placerade mellan 50-170 cm över marken. Det är en fin mörk typisk granskog. Skulle bli glad om någon kunde kolla på dessa bilder och lämna en kommentar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103623609</v>
+        <v>99621504</v>
       </c>
       <c r="B12" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,36 +1736,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560579.158871153</v>
+        <v>560607</v>
       </c>
       <c r="R12" t="n">
-        <v>6842147.064218552</v>
+        <v>6842105</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1912,22 +1797,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,67 +1839,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104778126</v>
+        <v>99622300</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Uppe i slänten från cykelbanan sett. Vid och delvis under en samling lågor., Hls</t>
+          <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560605.2104017724</v>
+        <v>560536</v>
       </c>
       <c r="R13" t="n">
-        <v>6842070.670683379</v>
+        <v>6842187</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,22 +1911,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,79 +1931,67 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Niklas Paulsson</t>
+          <t>Fredrik Robertsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Niklas Paulsson</t>
+          <t>Fredrik Robertsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104778087</v>
+        <v>99622332</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>På vallen (utsidan) ned från en kolbotten, 1-2 kliv ner från toppen av vall, Hls</t>
+          <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560634.0121741431</v>
+        <v>560575</v>
       </c>
       <c r="R14" t="n">
-        <v>6842161.787939053</v>
+        <v>6842182</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2164,22 +2015,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,12 +2045,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Niklas Paulsson</t>
+          <t>Fredrik Robertsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Niklas Paulsson</t>
+          <t>Fredrik Robertsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2209,12 +2060,7 @@
         <v>99637714</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560568.3349171596</v>
+        <v>560569</v>
       </c>
       <c r="R15" t="n">
-        <v>6842141.1809227</v>
+        <v>6842141</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2325,15 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99622332</v>
+        <v>103623609</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,29 +2182,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2372,10 +2220,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560574.7412204138</v>
+        <v>560580</v>
       </c>
       <c r="R16" t="n">
-        <v>6842182.09126399</v>
+        <v>6842147</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2402,22 +2250,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,60 +2282,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99621504</v>
+        <v>99520623</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ljusdal, Hls</t>
+          <t>Bad1, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560607.9420015299</v>
+        <v>560575</v>
       </c>
       <c r="R17" t="n">
-        <v>6842104.401235471</v>
+        <v>6842063</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,22 +2351,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,6 +2365,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2563,57 +2384,47 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99622300</v>
+        <v>99638154</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560535.7028477064</v>
+        <v>560590</v>
       </c>
       <c r="R18" t="n">
-        <v>6842186.622337937</v>
+        <v>6842051</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2640,22 +2451,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,61 +2493,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98548616</v>
+        <v>103626894</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Badtjärn, Hls</t>
+          <t>Ljusdal, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560579.9188319806</v>
+        <v>560575</v>
       </c>
       <c r="R19" t="n">
-        <v>6842103.907651271</v>
+        <v>6842067</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,22 +2563,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,6 +2602,955 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104778087</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>På vallen (utsidan) ned från en kolbotten, 1-2 kliv ner från toppen av vall, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>560634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6842162</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Niklas Paulsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niklas Paulsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104778105</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Uppe i slänten från cykelbanan sett. Vid och delvis under en samling lågor., Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>560605</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6842070</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Niklas Paulsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Niklas Paulsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>109298059</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Järvsöbaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>560704</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6842115</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>109299162</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Järvsöbaden, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>560691</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6842090</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>John Lindström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110553404</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kramsta, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>560656</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6842024</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>110553419</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kramsta, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>560672</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6842098</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110553578</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kramsta, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>560677</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6842082</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110553600</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kramsta, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>560683</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6842079</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En blomstängel från föregående blomning.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
